--- a/test/customervendor.xlsx
+++ b/test/customervendor.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28429"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Abhiraj Das\Documents\DMSBackend\test\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{30627319-7122-42AF-BAD8-3FD684A967BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6BC9663-2004-4BF4-B84F-B9FF98915344}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15390" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4470" yWindow="1200" windowWidth="22020" windowHeight="13515" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="52">
   <si>
     <t>name</t>
   </si>
@@ -49,9 +49,6 @@
     <t>contact</t>
   </si>
   <si>
-    <t>John Doe</t>
-  </si>
-  <si>
     <t>Jane Smith</t>
   </si>
   <si>
@@ -115,30 +112,6 @@
     <t>PAN2345678</t>
   </si>
   <si>
-    <t>PAN3456789</t>
-  </si>
-  <si>
-    <t>PAN4567890</t>
-  </si>
-  <si>
-    <t>PAN5678901</t>
-  </si>
-  <si>
-    <t>PAN6789012</t>
-  </si>
-  <si>
-    <t>PAN7890123</t>
-  </si>
-  <si>
-    <t>PAN8901234</t>
-  </si>
-  <si>
-    <t>PAN9012345</t>
-  </si>
-  <si>
-    <t>PAN0123456</t>
-  </si>
-  <si>
     <t>123 Street, City</t>
   </si>
   <si>
@@ -197,6 +170,12 @@
   </si>
   <si>
     <t>patricia@example.com</t>
+  </si>
+  <si>
+    <t>John Doe@@</t>
+  </si>
+  <si>
+    <t>ASDFG7412K</t>
   </si>
 </sst>
 </file>
@@ -598,16 +577,16 @@
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>9</v>
+        <v>50</v>
       </c>
       <c r="B2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D2" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="E2">
         <v>1</v>
@@ -619,7 +598,7 @@
         <v>0</v>
       </c>
       <c r="H2" t="s">
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="I2">
         <v>9876543210</v>
@@ -627,16 +606,16 @@
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B3" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D3" t="s">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="E3">
         <v>2</v>
@@ -648,7 +627,7 @@
         <v>1</v>
       </c>
       <c r="H3" t="s">
-        <v>50</v>
+        <v>41</v>
       </c>
       <c r="I3">
         <v>8765432109</v>
@@ -656,16 +635,16 @@
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B4" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C4" t="s">
-        <v>31</v>
+        <v>51</v>
       </c>
       <c r="D4" t="s">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="E4">
         <v>3</v>
@@ -677,7 +656,7 @@
         <v>1</v>
       </c>
       <c r="H4" t="s">
-        <v>51</v>
+        <v>42</v>
       </c>
       <c r="I4">
         <v>7654321098</v>
@@ -685,16 +664,16 @@
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C5" t="s">
-        <v>32</v>
+        <v>51</v>
       </c>
       <c r="D5" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="E5">
         <v>4</v>
@@ -706,7 +685,7 @@
         <v>1</v>
       </c>
       <c r="H5" t="s">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="I5">
         <v>6543210987</v>
@@ -714,16 +693,16 @@
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C6" t="s">
-        <v>33</v>
+        <v>51</v>
       </c>
       <c r="D6" t="s">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="E6">
         <v>5</v>
@@ -735,7 +714,7 @@
         <v>0</v>
       </c>
       <c r="H6" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="I6">
         <v>5432109876</v>
@@ -743,16 +722,16 @@
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B7" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C7" t="s">
-        <v>34</v>
+        <v>51</v>
       </c>
       <c r="D7" t="s">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="E7">
         <v>6</v>
@@ -764,7 +743,7 @@
         <v>1</v>
       </c>
       <c r="H7" t="s">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="I7">
         <v>4321098765</v>
@@ -772,16 +751,16 @@
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B8" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C8" t="s">
-        <v>35</v>
+        <v>51</v>
       </c>
       <c r="D8" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="E8">
         <v>7</v>
@@ -793,7 +772,7 @@
         <v>0</v>
       </c>
       <c r="H8" t="s">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="I8">
         <v>3210987654</v>
@@ -801,16 +780,16 @@
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B9" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C9" t="s">
-        <v>36</v>
+        <v>51</v>
       </c>
       <c r="D9" t="s">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="E9">
         <v>8</v>
@@ -822,7 +801,7 @@
         <v>1</v>
       </c>
       <c r="H9" t="s">
-        <v>56</v>
+        <v>47</v>
       </c>
       <c r="I9">
         <v>2109876543</v>
@@ -830,16 +809,16 @@
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B10" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C10" t="s">
-        <v>37</v>
+        <v>51</v>
       </c>
       <c r="D10" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="E10">
         <v>9</v>
@@ -851,7 +830,7 @@
         <v>1</v>
       </c>
       <c r="H10" t="s">
-        <v>57</v>
+        <v>48</v>
       </c>
       <c r="I10">
         <v>1098765432</v>
@@ -859,16 +838,16 @@
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B11" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C11" t="s">
-        <v>38</v>
+        <v>51</v>
       </c>
       <c r="D11" t="s">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="E11">
         <v>10</v>
@@ -880,7 +859,7 @@
         <v>1</v>
       </c>
       <c r="H11" t="s">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="I11">
         <v>9988776655</v>
